--- a/data/2026/cjsl/fall/south-brooklyn-fc-2-2013-2014.xlsx
+++ b/data/2026/cjsl/fall/south-brooklyn-fc-2-2013-2014.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="45.1"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="55.00000000000001"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="18.700000000000003"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="5.5"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/south-brooklyn-fc-2-2013-2014.xlsx
+++ b/data/2026/cjsl/fall/south-brooklyn-fc-2-2013-2014.xlsx
@@ -74,7 +74,7 @@
     <col min="2" max="2" bestFit="1" customWidth="1" width="28.6"/>
     <col min="3" max="3" bestFit="1" customWidth="1" width="13.200000000000001"/>
     <col min="4" max="4" bestFit="1" customWidth="1" width="47.300000000000004"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" width="7.700000000000001"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" width="8.8"/>
     <col min="6" max="6" bestFit="1" customWidth="1" width="45.1"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="55.00000000000001"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="18.700000000000003"/>
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 - 0</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/south-brooklyn-fc-2-2013-2014.xlsx
+++ b/data/2026/cjsl/fall/south-brooklyn-fc-2-2013-2014.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="45.1"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="55.00000000000001"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="18.700000000000003"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="12.100000000000001"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -175,36 +175,36 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Saturday, September 26, 2026</t>
+          <t>Sunday, October  4, 2026</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>16:30 EDT</t>
+          <t>14:00 EDT</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Ajer</t>
+          <t>South Brooklyn FC #2 2013/2014</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 - 0</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>South Brooklyn FC #2 2013/2014</t>
+          <t>Dynamo Soccer Club 2014</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Dyker Turf Field A Small Sided  - A</t>
+          <t>Bush Terminal Park - Bush Terminal #2 11v11</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -214,42 +214,42 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>Rained Out</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Sunday, October  4, 2026</t>
+          <t>Saturday, October 17, 2026</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>14:00 EDT</t>
+          <t>10:35 EDT</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>South Brooklyn FC #2 2013/2014</t>
+          <t>NY Kids S.C. 2013/2014 boys</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>10 - 0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>Dynamo Soccer Club 2014</t>
+          <t>South Brooklyn FC #2 2013/2014</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>Bush Terminal Park - Bush Terminal #2 11v11</t>
+          <t>Grover Cleveland Playground - Grover Cleveland Playground: Soccer-01</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -265,21 +265,21 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 17, 2026</t>
+          <t>Saturday, October 24, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>10:35 EDT</t>
+          <t>17:30 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>NY Kids S.C. 2013/2014 boys</t>
+          <t>South Brooklyn FC #2 2013/2014</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -289,12 +289,12 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>South Brooklyn FC #2 2013/2014</t>
+          <t>Brooklyn United Academy B2013/2014 Park Slope Select</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>Grover Cleveland Playground - Grover Cleveland Playground: Soccer-01</t>
+          <t>Calvert Vaux/Verrazano Complex - Field #1</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -310,21 +310,21 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 24, 2026</t>
+          <t>Sunday, October 25, 2026</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>17:30 EDT</t>
+          <t>13:30 EDT</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>South Brooklyn FC #2 2013/2014</t>
+          <t>SC Gjoa Ajer</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -334,12 +334,12 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>Brooklyn United Academy B2013/2014 Park Slope Select</t>
+          <t>South Brooklyn FC #2 2013/2014</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>Calvert Vaux/Verrazano Complex - Field #1</t>
+          <t>Dyker Turf Field B Small Sided  - B</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -349,7 +349,7 @@
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/south-brooklyn-fc-2-2013-2014.xlsx
+++ b/data/2026/cjsl/fall/south-brooklyn-fc-2-2013-2014.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 - 6</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/south-brooklyn-fc-2-2013-2014.xlsx
+++ b/data/2026/cjsl/fall/south-brooklyn-fc-2-2013-2014.xlsx
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4 - 1</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
@@ -329,7 +329,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 - 7</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
